--- a/public/EXPORTING_FILE.xlsx
+++ b/public/EXPORTING_FILE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AFMS-GASU\Desktop\HRMU\react-hrmu\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9352881-47A6-4E4C-B398-D266ACE4836A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86892252-70A8-42E5-9ABC-87EFE5396CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,12 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>STATUS OF LEAVE CREDITS</t>
-  </si>
-  <si>
-    <t>AS OF JANUARY 2023</t>
   </si>
   <si>
     <t>OCD CARAGA</t>
@@ -413,6 +410,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -458,7 +456,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,128 +697,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="30"/>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="30"/>
+    </row>
+    <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="29"/>
-    </row>
-    <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="37" t="s">
+      <c r="L3" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="M3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="23"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="25" t="s">
+      <c r="Q3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="35" t="s">
+    </row>
+    <row r="4" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="34"/>
-      <c r="L4" s="26"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="27"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
     </row>
     <row r="5" spans="1:27" ht="49.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8"/>
@@ -846,7 +841,7 @@
         <v>#REF!</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
@@ -1342,16 +1337,16 @@
       <c r="O21" s="5"/>
       <c r="P21" s="10"/>
       <c r="Q21" s="11"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="39"/>
-      <c r="T21" s="39"/>
-      <c r="U21" s="39"/>
-      <c r="V21" s="39"/>
-      <c r="W21" s="39"/>
-      <c r="X21" s="39"/>
-      <c r="Y21" s="39"/>
-      <c r="Z21" s="39"/>
-      <c r="AA21" s="39"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
     </row>
     <row r="22" spans="1:27" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -1371,16 +1366,16 @@
       <c r="O22" s="5"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="11"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="39"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="39"/>
-      <c r="W22" s="39"/>
-      <c r="X22" s="39"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39"/>
-      <c r="AA22" s="39"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
     </row>
     <row r="23" spans="1:27" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
@@ -1400,16 +1395,16 @@
       <c r="O23" s="5"/>
       <c r="P23" s="10"/>
       <c r="Q23" s="11"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="39"/>
-      <c r="U23" s="39"/>
-      <c r="V23" s="39"/>
-      <c r="W23" s="39"/>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39"/>
-      <c r="AA23" s="39"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="18"/>
+      <c r="AA23" s="18"/>
     </row>
     <row r="24" spans="1:27" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
@@ -1429,16 +1424,16 @@
       <c r="O24" s="5"/>
       <c r="P24" s="10"/>
       <c r="Q24" s="11"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="39"/>
-      <c r="W24" s="39"/>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="39"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
     </row>
     <row r="25" spans="1:27" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
@@ -1458,16 +1453,16 @@
       <c r="O25" s="5"/>
       <c r="P25" s="10"/>
       <c r="Q25" s="11"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="39"/>
-      <c r="T25" s="39"/>
-      <c r="U25" s="39"/>
-      <c r="V25" s="39"/>
-      <c r="W25" s="39"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="39"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="18"/>
     </row>
     <row r="26" spans="1:27" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -1487,16 +1482,16 @@
       <c r="O26" s="5"/>
       <c r="P26" s="10"/>
       <c r="Q26" s="11"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="39"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="39"/>
-      <c r="W26" s="39"/>
-      <c r="X26" s="39"/>
-      <c r="Y26" s="39"/>
-      <c r="Z26" s="39"/>
-      <c r="AA26" s="39"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="18"/>
     </row>
     <row r="27" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
@@ -1640,16 +1635,16 @@
       <c r="O31" s="5"/>
       <c r="P31" s="10"/>
       <c r="Q31" s="11"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
-      <c r="T31" s="39"/>
-      <c r="U31" s="39"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="39"/>
-      <c r="X31" s="39"/>
-      <c r="Y31" s="39"/>
-      <c r="Z31" s="39"/>
-      <c r="AA31" s="39"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="18"/>
+      <c r="Z31" s="18"/>
+      <c r="AA31" s="18"/>
     </row>
     <row r="32" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
@@ -1683,148 +1678,148 @@
       <c r="AA32" s="12"/>
     </row>
     <row r="33" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="18"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
     </row>
     <row r="34" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="20"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
     </row>
     <row r="35" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="20"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
     </row>
     <row r="36" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="20"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
     </row>
     <row r="37" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="20"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
     </row>
     <row r="38" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="20"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
     </row>
     <row r="39" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="20"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22"/>
     </row>
     <row r="40" spans="2:17" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="20"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22"/>
     </row>
     <row r="41" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P41" s="12"/>
